--- a/data/satisfaction_detail/2026/1-6月/展览主承办.xlsx
+++ b/data/satisfaction_detail/2026/1-6月/展览主承办.xlsx
@@ -472,10 +472,10 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>9.4</v>
+        <v>9.43</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>9.710000000000001</v>
+        <v>9.67</v>
       </c>
     </row>
     <row r="3">
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>9.859999999999999</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="C4" s="4" t="n">
         <v>10</v>
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>9.859999999999999</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>10</v>
@@ -553,7 +553,7 @@
         <v>9.9</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>9.76</v>
+        <v>9.77</v>
       </c>
     </row>
     <row r="9">
@@ -579,7 +579,7 @@
         <v>9.970000000000001</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>9.970000000000001</v>
+        <v>9.93</v>
       </c>
     </row>
     <row r="11">
@@ -602,10 +602,10 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>9.48</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>9.619999999999999</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="13">
@@ -618,7 +618,7 @@
         <v>9.970000000000001</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>9.859999999999999</v>
+        <v>9.869999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -693,10 +693,10 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>9.460000000000001</v>
+        <v>9.44</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>9.949999999999999</v>
+        <v>9.93</v>
       </c>
     </row>
     <row r="20">
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>9.66</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>9.970000000000001</v>
+        <v>9.93</v>
       </c>
     </row>
     <row r="21">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>9.449999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>9.970000000000001</v>
+        <v>9.93</v>
       </c>
     </row>
     <row r="22">
@@ -732,10 +732,10 @@
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>9.52</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>9.970000000000001</v>
+        <v>9.93</v>
       </c>
     </row>
     <row r="23">
@@ -745,10 +745,10 @@
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>9.789999999999999</v>
+        <v>9.77</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>9.970000000000001</v>
+        <v>9.93</v>
       </c>
     </row>
     <row r="24">
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>9.31</v>
+        <v>9.27</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>10</v>
+        <v>9.970000000000001</v>
       </c>
     </row>
     <row r="25">
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>9.380000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>9.93</v>
@@ -784,10 +784,10 @@
         </is>
       </c>
       <c r="B26" s="4" t="n">
-        <v>9.140000000000001</v>
+        <v>9.17</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>9.859999999999999</v>
+        <v>9.869999999999999</v>
       </c>
     </row>
     <row r="27">
@@ -797,10 +797,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>9.73</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>9.949999999999999</v>
+        <v>9.94</v>
       </c>
     </row>
     <row r="28">
@@ -810,10 +810,10 @@
         </is>
       </c>
       <c r="B28" s="4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.15</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>9.92</v>
+        <v>9.880000000000001</v>
       </c>
     </row>
     <row r="29">
@@ -862,10 +862,10 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>8.5</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>9</v>
+        <v>8.880000000000001</v>
       </c>
     </row>
     <row r="33">
@@ -891,7 +891,7 @@
         <v>9</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="35">
@@ -901,7 +901,7 @@
         </is>
       </c>
       <c r="B35" s="4" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>9</v>
